--- a/data/workbook/מעקב מחירי מזון.xlsx
+++ b/data/workbook/מעקב מחירי מזון.xlsx
@@ -1641,7 +1641,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1697,7 +1697,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1753,7 +1753,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1809,7 +1809,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1865,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1921,7 +1921,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1977,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2005,7 +2005,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2033,7 +2033,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2061,7 +2061,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2089,7 +2089,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2145,7 +2145,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2285,7 +2285,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2397,7 +2397,7 @@
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2425,7 +2425,7 @@
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2453,7 +2453,7 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2481,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2509,7 +2509,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2537,7 +2537,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2621,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2649,7 +2649,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2677,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2705,7 +2705,7 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2733,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2761,7 +2761,7 @@
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2817,7 +2817,7 @@
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2845,7 +2845,7 @@
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2873,7 +2873,7 @@
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2901,7 +2901,7 @@
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3041,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3153,7 +3153,7 @@
         <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3209,7 +3209,7 @@
         <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3237,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3293,7 +3293,7 @@
         <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3377,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3405,7 +3405,7 @@
         <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3489,7 +3489,7 @@
         <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3517,7 +3517,7 @@
         <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3601,7 +3601,7 @@
         <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -3629,7 +3629,7 @@
         <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3657,7 +3657,7 @@
         <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3713,7 +3713,7 @@
         <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -3741,7 +3741,7 @@
         <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -3797,7 +3797,7 @@
         <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -3825,7 +3825,7 @@
         <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3853,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3881,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3909,7 +3909,7 @@
         <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -3937,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3965,7 +3965,7 @@
         <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4077,7 +4077,7 @@
         <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4105,7 +4105,7 @@
         <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4161,7 +4161,7 @@
         <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4217,7 +4217,7 @@
         <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4245,7 +4245,7 @@
         <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4301,7 +4301,7 @@
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -4329,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4357,7 +4357,7 @@
         <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -4525,7 +4525,7 @@
         <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -4553,7 +4553,7 @@
         <v>3</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -4581,7 +4581,7 @@
         <v>3</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4609,7 +4609,7 @@
         <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -4637,7 +4637,7 @@
         <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -4665,7 +4665,7 @@
         <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -4693,7 +4693,7 @@
         <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -4721,7 +4721,7 @@
         <v>3</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -4749,7 +4749,7 @@
         <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -4777,7 +4777,7 @@
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -4833,7 +4833,7 @@
         <v>6</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -4861,7 +4861,7 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -4945,7 +4945,7 @@
         <v>6</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -4973,7 +4973,7 @@
         <v>6</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5001,7 +5001,7 @@
         <v>6</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5029,8 +5029,8 @@
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5217,8 +5217,11 @@
       <c r="H5" t="n">
         <v>12.5</v>
       </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
       <c r="J5" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -5518,8 +5521,11 @@
       <c r="H12" t="n">
         <v>7.9</v>
       </c>
+      <c r="I12" t="n">
+        <v>6.666666666666667</v>
+      </c>
       <c r="J12" t="n">
-        <v>7.9</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -5561,8 +5567,11 @@
       <c r="H13" t="n">
         <v>7.9</v>
       </c>
+      <c r="I13" t="n">
+        <v>6.666666666666667</v>
+      </c>
       <c r="J13" t="n">
-        <v>7.9</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -5604,8 +5613,11 @@
       <c r="H14" t="n">
         <v>6.5</v>
       </c>
+      <c r="I14" t="n">
+        <v>5.45</v>
+      </c>
       <c r="J14" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="15">
@@ -5991,8 +6003,11 @@
       <c r="H23" t="n">
         <v>49.9</v>
       </c>
+      <c r="I23" t="n">
+        <v>35</v>
+      </c>
       <c r="J23" t="n">
-        <v>49.9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -6034,8 +6049,11 @@
       <c r="H24" t="n">
         <v>49.9</v>
       </c>
+      <c r="I24" t="n">
+        <v>35</v>
+      </c>
       <c r="J24" t="n">
-        <v>49.9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
@@ -6163,8 +6181,11 @@
       <c r="H27" t="n">
         <v>30.9</v>
       </c>
+      <c r="I27" t="n">
+        <v>25</v>
+      </c>
       <c r="J27" t="n">
-        <v>30.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -6206,6 +6227,9 @@
       <c r="H28" t="n">
         <v>34.9</v>
       </c>
+      <c r="I28" t="n">
+        <v>34.9</v>
+      </c>
       <c r="J28" t="n">
         <v>34.9</v>
       </c>
@@ -6249,8 +6273,11 @@
       <c r="H29" t="n">
         <v>25.9</v>
       </c>
+      <c r="I29" t="n">
+        <v>22.5</v>
+      </c>
       <c r="J29" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="30">
@@ -6378,8 +6405,11 @@
       <c r="H32" t="n">
         <v>29.9</v>
       </c>
+      <c r="I32" t="n">
+        <v>25</v>
+      </c>
       <c r="J32" t="n">
-        <v>29.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -6421,8 +6451,11 @@
       <c r="H33" t="n">
         <v>18.9</v>
       </c>
+      <c r="I33" t="n">
+        <v>14</v>
+      </c>
       <c r="J33" t="n">
-        <v>18.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -6894,8 +6927,11 @@
       <c r="H44" t="n">
         <v>7.9</v>
       </c>
+      <c r="I44" t="n">
+        <v>5.333333333333333</v>
+      </c>
       <c r="J44" t="n">
-        <v>7.9</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -7324,8 +7360,11 @@
       <c r="H54" t="n">
         <v>32.9</v>
       </c>
+      <c r="I54" t="n">
+        <v>28.9</v>
+      </c>
       <c r="J54" t="n">
-        <v>32.9</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="55">
@@ -7367,8 +7406,11 @@
       <c r="H55" t="n">
         <v>26.9</v>
       </c>
+      <c r="I55" t="n">
+        <v>22</v>
+      </c>
       <c r="J55" t="n">
-        <v>26.9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -7410,8 +7452,11 @@
       <c r="H56" t="n">
         <v>25.9</v>
       </c>
+      <c r="I56" t="n">
+        <v>22.5</v>
+      </c>
       <c r="J56" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="57">
@@ -7453,8 +7498,11 @@
       <c r="H57" t="n">
         <v>5.9</v>
       </c>
+      <c r="I57" t="n">
+        <v>3.333333333333333</v>
+      </c>
       <c r="J57" t="n">
-        <v>5.9</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -7496,8 +7544,11 @@
       <c r="H58" t="n">
         <v>6.9</v>
       </c>
+      <c r="I58" t="n">
+        <v>6</v>
+      </c>
       <c r="J58" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -7582,8 +7633,11 @@
       <c r="H60" t="n">
         <v>45.9</v>
       </c>
+      <c r="I60" t="n">
+        <v>38.9</v>
+      </c>
       <c r="J60" t="n">
-        <v>45.9</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="61">
@@ -7883,8 +7937,11 @@
       <c r="H67" t="n">
         <v>14.2</v>
       </c>
+      <c r="I67" t="n">
+        <v>11</v>
+      </c>
       <c r="J67" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -7969,8 +8026,11 @@
       <c r="H69" t="n">
         <v>6.9</v>
       </c>
+      <c r="I69" t="n">
+        <v>6.45</v>
+      </c>
       <c r="J69" t="n">
-        <v>6.9</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="70">
@@ -8184,8 +8244,11 @@
       <c r="H74" t="n">
         <v>11</v>
       </c>
+      <c r="I74" t="n">
+        <v>8.333333333333334</v>
+      </c>
       <c r="J74" t="n">
-        <v>11</v>
+        <v>8.333333333333334</v>
       </c>
     </row>
     <row r="75">
@@ -8399,8 +8462,11 @@
       <c r="H79" t="n">
         <v>14.9</v>
       </c>
+      <c r="I79" t="n">
+        <v>10</v>
+      </c>
       <c r="J79" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -8571,8 +8637,11 @@
       <c r="H83" t="n">
         <v>8.9</v>
       </c>
+      <c r="I83" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J83" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="84">
@@ -8614,8 +8683,11 @@
       <c r="H84" t="n">
         <v>12.9</v>
       </c>
+      <c r="I84" t="n">
+        <v>12.26</v>
+      </c>
       <c r="J84" t="n">
-        <v>12.9</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="85">
@@ -8657,8 +8729,11 @@
       <c r="H85" t="n">
         <v>5.9</v>
       </c>
+      <c r="I85" t="n">
+        <v>5.61</v>
+      </c>
       <c r="J85" t="n">
-        <v>5.9</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="86">
@@ -8872,8 +8947,11 @@
       <c r="H90" t="n">
         <v>8.9</v>
       </c>
+      <c r="I90" t="n">
+        <v>8.460000000000001</v>
+      </c>
       <c r="J90" t="n">
-        <v>8.9</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -9216,8 +9294,11 @@
       <c r="H98" t="n">
         <v>10.9</v>
       </c>
+      <c r="I98" t="n">
+        <v>9.9</v>
+      </c>
       <c r="J98" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="99">
@@ -9302,8 +9383,11 @@
       <c r="H100" t="n">
         <v>6.5</v>
       </c>
+      <c r="I100" t="n">
+        <v>5</v>
+      </c>
       <c r="J100" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -9431,8 +9515,11 @@
       <c r="H103" t="n">
         <v>24.9</v>
       </c>
+      <c r="I103" t="n">
+        <v>19.9</v>
+      </c>
       <c r="J103" t="n">
-        <v>24.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="104">
@@ -9474,8 +9561,11 @@
       <c r="H104" t="n">
         <v>7.9</v>
       </c>
+      <c r="I104" t="n">
+        <v>7</v>
+      </c>
       <c r="J104" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -9603,8 +9693,11 @@
       <c r="H107" t="n">
         <v>5</v>
       </c>
+      <c r="I107" t="n">
+        <v>4.5</v>
+      </c>
       <c r="J107" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="108">
@@ -9646,8 +9739,11 @@
       <c r="H108" t="n">
         <v>9</v>
       </c>
+      <c r="I108" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="109">
@@ -9732,8 +9828,11 @@
       <c r="H110" t="n">
         <v>5.9</v>
       </c>
+      <c r="I110" t="n">
+        <v>4</v>
+      </c>
       <c r="J110" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -9775,8 +9874,11 @@
       <c r="H111" t="n">
         <v>34.9</v>
       </c>
+      <c r="I111" t="n">
+        <v>25</v>
+      </c>
       <c r="J111" t="n">
-        <v>34.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112">
@@ -9904,8 +10006,11 @@
       <c r="H114" t="n">
         <v>37.9</v>
       </c>
+      <c r="I114" t="n">
+        <v>34.9</v>
+      </c>
       <c r="J114" t="n">
-        <v>37.9</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="115">
@@ -9947,8 +10052,11 @@
       <c r="H115" t="n">
         <v>44.9</v>
       </c>
+      <c r="I115" t="n">
+        <v>27.9</v>
+      </c>
       <c r="J115" t="n">
-        <v>44.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="116">
@@ -9990,8 +10098,11 @@
       <c r="H116" t="n">
         <v>44.9</v>
       </c>
+      <c r="I116" t="n">
+        <v>27.9</v>
+      </c>
       <c r="J116" t="n">
-        <v>44.9</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="117">
@@ -10076,8 +10187,11 @@
       <c r="H118" t="n">
         <v>25.9</v>
       </c>
+      <c r="I118" t="n">
+        <v>24.9</v>
+      </c>
       <c r="J118" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="119">
@@ -10119,8 +10233,11 @@
       <c r="H119" t="n">
         <v>26.9</v>
       </c>
+      <c r="I119" t="n">
+        <v>25</v>
+      </c>
       <c r="J119" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120">
@@ -10162,8 +10279,11 @@
       <c r="H120" t="n">
         <v>34.9</v>
       </c>
+      <c r="I120" t="n">
+        <v>24.9</v>
+      </c>
       <c r="J120" t="n">
-        <v>34.9</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="121">
@@ -10205,8 +10325,11 @@
       <c r="H121" t="n">
         <v>33.9</v>
       </c>
+      <c r="I121" t="n">
+        <v>25</v>
+      </c>
       <c r="J121" t="n">
-        <v>33.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122">
@@ -10248,8 +10371,11 @@
       <c r="H122" t="n">
         <v>22.9</v>
       </c>
+      <c r="I122" t="n">
+        <v>19.9</v>
+      </c>
       <c r="J122" t="n">
-        <v>22.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="123">
@@ -10291,8 +10417,11 @@
       <c r="H123" t="n">
         <v>22.9</v>
       </c>
+      <c r="I123" t="n">
+        <v>19.9</v>
+      </c>
       <c r="J123" t="n">
-        <v>22.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="124">
@@ -10334,8 +10463,11 @@
       <c r="H124" t="n">
         <v>28.8</v>
       </c>
+      <c r="I124" t="n">
+        <v>25</v>
+      </c>
       <c r="J124" t="n">
-        <v>28.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
@@ -10377,8 +10509,11 @@
       <c r="H125" t="n">
         <v>16.9</v>
       </c>
+      <c r="I125" t="n">
+        <v>12.9</v>
+      </c>
       <c r="J125" t="n">
-        <v>16.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="126">
@@ -10420,8 +10555,11 @@
       <c r="H126" t="n">
         <v>45.3</v>
       </c>
+      <c r="I126" t="n">
+        <v>39.9</v>
+      </c>
       <c r="J126" t="n">
-        <v>45.3</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="127">
@@ -10850,8 +10988,11 @@
       <c r="H136" t="n">
         <v>6.2</v>
       </c>
+      <c r="I136" t="n">
+        <v>5</v>
+      </c>
       <c r="J136" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
@@ -10893,8 +11034,11 @@
       <c r="H137" t="n">
         <v>8</v>
       </c>
+      <c r="I137" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J137" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="138">
@@ -11108,8 +11252,11 @@
       <c r="H142" t="n">
         <v>9.300000000000001</v>
       </c>
+      <c r="I142" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J142" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="143">
@@ -11237,8 +11384,11 @@
       <c r="H145" t="n">
         <v>19.9</v>
       </c>
+      <c r="I145" t="n">
+        <v>16.9</v>
+      </c>
       <c r="J145" t="n">
-        <v>19.9</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="146">
@@ -11323,8 +11473,11 @@
       <c r="H147" t="n">
         <v>22.9</v>
       </c>
+      <c r="I147" t="n">
+        <v>18</v>
+      </c>
       <c r="J147" t="n">
-        <v>22.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148">
@@ -11366,8 +11519,11 @@
       <c r="H148" t="n">
         <v>25.9</v>
       </c>
+      <c r="I148" t="n">
+        <v>20</v>
+      </c>
       <c r="J148" t="n">
-        <v>25.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149">
@@ -11409,8 +11565,11 @@
       <c r="H149" t="n">
         <v>4.9</v>
       </c>
+      <c r="I149" t="n">
+        <v>3.333333333333333</v>
+      </c>
       <c r="J149" t="n">
-        <v>4.9</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="150">
@@ -11452,8 +11611,11 @@
       <c r="H150" t="n">
         <v>5.9</v>
       </c>
+      <c r="I150" t="n">
+        <v>4.9</v>
+      </c>
       <c r="J150" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="151">
@@ -11538,8 +11700,11 @@
       <c r="H152" t="n">
         <v>38.9</v>
       </c>
+      <c r="I152" t="n">
+        <v>34.9</v>
+      </c>
       <c r="J152" t="n">
-        <v>38.9</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="153">
@@ -11581,8 +11746,11 @@
       <c r="H153" t="n">
         <v>18.9</v>
       </c>
+      <c r="I153" t="n">
+        <v>15.9</v>
+      </c>
       <c r="J153" t="n">
-        <v>18.9</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="154">
@@ -11753,8 +11921,11 @@
       <c r="H157" t="n">
         <v>18.9</v>
       </c>
+      <c r="I157" t="n">
+        <v>16.9</v>
+      </c>
       <c r="J157" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="158">
@@ -11839,8 +12010,11 @@
       <c r="H159" t="n">
         <v>13.2</v>
       </c>
+      <c r="I159" t="n">
+        <v>8</v>
+      </c>
       <c r="J159" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160">
@@ -12097,8 +12271,11 @@
       <c r="H165" t="n">
         <v>7.5</v>
       </c>
+      <c r="I165" t="n">
+        <v>6.5</v>
+      </c>
       <c r="J165" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="166">
@@ -12140,8 +12317,11 @@
       <c r="H166" t="n">
         <v>8.9</v>
       </c>
+      <c r="I166" t="n">
+        <v>8.333333333333334</v>
+      </c>
       <c r="J166" t="n">
-        <v>8.9</v>
+        <v>8.333333333333334</v>
       </c>
     </row>
     <row r="167">
@@ -12312,8 +12492,11 @@
       <c r="H170" t="n">
         <v>17.9</v>
       </c>
+      <c r="I170" t="n">
+        <v>14.9</v>
+      </c>
       <c r="J170" t="n">
-        <v>17.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="171">
@@ -12355,8 +12538,11 @@
       <c r="H171" t="n">
         <v>11.9</v>
       </c>
+      <c r="I171" t="n">
+        <v>9.9</v>
+      </c>
       <c r="J171" t="n">
-        <v>11.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="172">
@@ -12484,8 +12670,11 @@
       <c r="H174" t="n">
         <v>7.9</v>
       </c>
+      <c r="I174" t="n">
+        <v>4.9</v>
+      </c>
       <c r="J174" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="175">
@@ -12527,8 +12716,11 @@
       <c r="H175" t="n">
         <v>8.5</v>
       </c>
+      <c r="I175" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J175" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="176">
@@ -12570,8 +12762,11 @@
       <c r="H176" t="n">
         <v>9.9</v>
       </c>
+      <c r="I176" t="n">
+        <v>9</v>
+      </c>
       <c r="J176" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177">
@@ -12613,8 +12808,11 @@
       <c r="H177" t="n">
         <v>14.9</v>
       </c>
+      <c r="I177" t="n">
+        <v>10</v>
+      </c>
       <c r="J177" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178">
@@ -12656,8 +12854,11 @@
       <c r="H178" t="n">
         <v>14.9</v>
       </c>
+      <c r="I178" t="n">
+        <v>10</v>
+      </c>
       <c r="J178" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
@@ -12699,8 +12900,11 @@
       <c r="H179" t="n">
         <v>5.9</v>
       </c>
+      <c r="I179" t="n">
+        <v>2.9</v>
+      </c>
       <c r="J179" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="180">
@@ -12957,8 +13161,11 @@
       <c r="H185" t="n">
         <v>3.3</v>
       </c>
+      <c r="I185" t="n">
+        <v>2.9</v>
+      </c>
       <c r="J185" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="186">
@@ -13301,8 +13508,11 @@
       <c r="H193" t="n">
         <v>13.5</v>
       </c>
+      <c r="I193" t="n">
+        <v>10</v>
+      </c>
       <c r="J193" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194">
@@ -13430,8 +13640,11 @@
       <c r="H196" t="n">
         <v>9.9</v>
       </c>
+      <c r="I196" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J196" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="197">
@@ -13473,8 +13686,11 @@
       <c r="H197" t="n">
         <v>13.5</v>
       </c>
+      <c r="I197" t="n">
+        <v>6.75</v>
+      </c>
       <c r="J197" t="n">
-        <v>13.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="198">
@@ -13516,8 +13732,11 @@
       <c r="H198" t="n">
         <v>27.9</v>
       </c>
+      <c r="I198" t="n">
+        <v>13.95</v>
+      </c>
       <c r="J198" t="n">
-        <v>27.9</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="199">
@@ -13688,8 +13907,11 @@
       <c r="H202" t="n">
         <v>6.5</v>
       </c>
+      <c r="I202" t="n">
+        <v>5</v>
+      </c>
       <c r="J202" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
@@ -13731,8 +13953,11 @@
       <c r="H203" t="n">
         <v>11.5</v>
       </c>
+      <c r="I203" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J203" t="n">
-        <v>11.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="204">
@@ -13817,8 +14042,11 @@
       <c r="H205" t="n">
         <v>6.9</v>
       </c>
+      <c r="I205" t="n">
+        <v>5.45</v>
+      </c>
       <c r="J205" t="n">
-        <v>6.9</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="206">
@@ -14032,8 +14260,11 @@
       <c r="H210" t="n">
         <v>39.9</v>
       </c>
+      <c r="I210" t="n">
+        <v>37.5</v>
+      </c>
       <c r="J210" t="n">
-        <v>39.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="211">
@@ -14075,8 +14306,11 @@
       <c r="H211" t="n">
         <v>49.9</v>
       </c>
+      <c r="I211" t="n">
+        <v>39.9</v>
+      </c>
       <c r="J211" t="n">
-        <v>49.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="212">
@@ -14118,8 +14352,11 @@
       <c r="H212" t="n">
         <v>49.9</v>
       </c>
+      <c r="I212" t="n">
+        <v>39.9</v>
+      </c>
       <c r="J212" t="n">
-        <v>49.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="213">
@@ -14290,8 +14527,11 @@
       <c r="H216" t="n">
         <v>28.9</v>
       </c>
+      <c r="I216" t="n">
+        <v>23</v>
+      </c>
       <c r="J216" t="n">
-        <v>28.9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -14505,8 +14745,11 @@
       <c r="H221" t="n">
         <v>22.9</v>
       </c>
+      <c r="I221" t="n">
+        <v>13.9</v>
+      </c>
       <c r="J221" t="n">
-        <v>22.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="222">
@@ -14548,8 +14791,11 @@
       <c r="H222" t="n">
         <v>54.9</v>
       </c>
+      <c r="I222" t="n">
+        <v>39.9</v>
+      </c>
       <c r="J222" t="n">
-        <v>54.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="223">
@@ -14935,8 +15181,11 @@
       <c r="H231" t="n">
         <v>7.9</v>
       </c>
+      <c r="I231" t="n">
+        <v>6.633333333333333</v>
+      </c>
       <c r="J231" t="n">
-        <v>7.9</v>
+        <v>6.633333333333333</v>
       </c>
     </row>
     <row r="232">
@@ -15408,8 +15657,11 @@
       <c r="H242" t="n">
         <v>29.9</v>
       </c>
+      <c r="I242" t="n">
+        <v>24.95</v>
+      </c>
       <c r="J242" t="n">
-        <v>29.9</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="243">
@@ -15494,8 +15746,11 @@
       <c r="H244" t="n">
         <v>5.9</v>
       </c>
+      <c r="I244" t="n">
+        <v>5.5</v>
+      </c>
       <c r="J244" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="245">
@@ -15537,8 +15792,11 @@
       <c r="H245" t="n">
         <v>6.9</v>
       </c>
+      <c r="I245" t="n">
+        <v>6</v>
+      </c>
       <c r="J245" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246">
@@ -15623,8 +15881,11 @@
       <c r="H247" t="n">
         <v>45.9</v>
       </c>
+      <c r="I247" t="n">
+        <v>37.9</v>
+      </c>
       <c r="J247" t="n">
-        <v>45.9</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="248">
@@ -15666,8 +15927,11 @@
       <c r="H248" t="n">
         <v>23.9</v>
       </c>
+      <c r="I248" t="n">
+        <v>18</v>
+      </c>
       <c r="J248" t="n">
-        <v>23.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="249">
@@ -16010,8 +16274,11 @@
       <c r="H256" t="n">
         <v>6.9</v>
       </c>
+      <c r="I256" t="n">
+        <v>5</v>
+      </c>
       <c r="J256" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
@@ -16182,8 +16449,11 @@
       <c r="H260" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="I260" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J260" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="261">
@@ -16225,8 +16495,11 @@
       <c r="H261" t="n">
         <v>10.9</v>
       </c>
+      <c r="I261" t="n">
+        <v>9</v>
+      </c>
       <c r="J261" t="n">
-        <v>10.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="262">
@@ -16397,8 +16670,11 @@
       <c r="H265" t="n">
         <v>17.9</v>
       </c>
+      <c r="I265" t="n">
+        <v>16.9</v>
+      </c>
       <c r="J265" t="n">
-        <v>17.9</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="266">
@@ -16569,8 +16845,11 @@
       <c r="H269" t="n">
         <v>9.9</v>
       </c>
+      <c r="I269" t="n">
+        <v>8.949999999999999</v>
+      </c>
       <c r="J269" t="n">
-        <v>9.9</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -16698,8 +16977,11 @@
       <c r="H272" t="n">
         <v>16.5</v>
       </c>
+      <c r="I272" t="n">
+        <v>14.95</v>
+      </c>
       <c r="J272" t="n">
-        <v>16.5</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="273">
@@ -16741,8 +17023,11 @@
       <c r="H273" t="n">
         <v>18.9</v>
       </c>
+      <c r="I273" t="n">
+        <v>14.95</v>
+      </c>
       <c r="J273" t="n">
-        <v>18.9</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="274">
@@ -17128,8 +17413,11 @@
       <c r="H282" t="n">
         <v>29.9</v>
       </c>
+      <c r="I282" t="n">
+        <v>29.08</v>
+      </c>
       <c r="J282" t="n">
-        <v>29.9</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="283">
@@ -17859,8 +18147,11 @@
       <c r="H299" t="n">
         <v>6.9</v>
       </c>
+      <c r="I299" t="n">
+        <v>4.5</v>
+      </c>
       <c r="J299" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="300">
@@ -18289,8 +18580,11 @@
       <c r="H309" t="n">
         <v>28.2</v>
       </c>
+      <c r="I309" t="n">
+        <v>24.9</v>
+      </c>
       <c r="J309" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="310">
@@ -18590,8 +18884,11 @@
       <c r="H316" t="n">
         <v>30.2</v>
       </c>
+      <c r="I316" t="n">
+        <v>25</v>
+      </c>
       <c r="J316" t="n">
-        <v>30.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="317">
@@ -18633,8 +18930,11 @@
       <c r="H317" t="n">
         <v>18.1</v>
       </c>
+      <c r="I317" t="n">
+        <v>14</v>
+      </c>
       <c r="J317" t="n">
-        <v>18.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="318">
@@ -18891,8 +19191,11 @@
       <c r="H323" t="n">
         <v>7.8</v>
       </c>
+      <c r="I323" t="n">
+        <v>5.9</v>
+      </c>
       <c r="J323" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="324">
@@ -19106,8 +19409,11 @@
       <c r="H328" t="n">
         <v>7.9</v>
       </c>
+      <c r="I328" t="n">
+        <v>5</v>
+      </c>
       <c r="J328" t="n">
-        <v>7.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329">
@@ -19321,8 +19627,11 @@
       <c r="H333" t="n">
         <v>9.5</v>
       </c>
+      <c r="I333" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J333" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="334">
@@ -19407,8 +19716,11 @@
       <c r="H335" t="n">
         <v>16.9</v>
       </c>
+      <c r="I335" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J335" t="n">
-        <v>16.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="336">
@@ -19579,8 +19891,11 @@
       <c r="H339" t="n">
         <v>24.9</v>
       </c>
+      <c r="I339" t="n">
+        <v>21.9</v>
+      </c>
       <c r="J339" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="340">
@@ -19622,8 +19937,11 @@
       <c r="H340" t="n">
         <v>30.9</v>
       </c>
+      <c r="I340" t="n">
+        <v>20</v>
+      </c>
       <c r="J340" t="n">
-        <v>30.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="341">
@@ -19665,8 +19983,11 @@
       <c r="H341" t="n">
         <v>5</v>
       </c>
+      <c r="I341" t="n">
+        <v>4</v>
+      </c>
       <c r="J341" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="342">
@@ -19708,8 +20029,11 @@
       <c r="H342" t="n">
         <v>7</v>
       </c>
+      <c r="I342" t="n">
+        <v>5</v>
+      </c>
       <c r="J342" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343">
@@ -19794,8 +20118,11 @@
       <c r="H344" t="n">
         <v>40.3</v>
       </c>
+      <c r="I344" t="n">
+        <v>34.9</v>
+      </c>
       <c r="J344" t="n">
-        <v>40.3</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="345">
@@ -19923,8 +20250,11 @@
       <c r="H347" t="n">
         <v>25.9</v>
       </c>
+      <c r="I347" t="n">
+        <v>21.5</v>
+      </c>
       <c r="J347" t="n">
-        <v>25.9</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="348">
@@ -20181,8 +20511,11 @@
       <c r="H353" t="n">
         <v>7.3</v>
       </c>
+      <c r="I353" t="n">
+        <v>6</v>
+      </c>
       <c r="J353" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354">
@@ -20740,8 +21073,11 @@
       <c r="H366" t="n">
         <v>9.9</v>
       </c>
+      <c r="I366" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J366" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="367">
@@ -20783,8 +21119,11 @@
       <c r="H367" t="n">
         <v>8.9</v>
       </c>
+      <c r="I367" t="n">
+        <v>8</v>
+      </c>
       <c r="J367" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -20826,8 +21165,11 @@
       <c r="H368" t="n">
         <v>12.1</v>
       </c>
+      <c r="I368" t="n">
+        <v>9</v>
+      </c>
       <c r="J368" t="n">
-        <v>12.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="369">
@@ -20869,8 +21211,11 @@
       <c r="H369" t="n">
         <v>16.1</v>
       </c>
+      <c r="I369" t="n">
+        <v>13</v>
+      </c>
       <c r="J369" t="n">
-        <v>16.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="370">
@@ -20912,8 +21257,11 @@
       <c r="H370" t="n">
         <v>14.9</v>
       </c>
+      <c r="I370" t="n">
+        <v>13</v>
+      </c>
       <c r="J370" t="n">
-        <v>14.9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="371">
